--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/32.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/32.xlsx
@@ -426,13 +426,13 @@
         <v>-7.661621455916652</v>
       </c>
       <c r="E2">
-        <v>-11.2075993823491</v>
+        <v>-8.329468856612104</v>
       </c>
       <c r="F2">
-        <v>-2.696524082760334</v>
+        <v>-1.909050693534832</v>
       </c>
       <c r="G2">
-        <v>-7.383587394886744</v>
+        <v>-5.998590337088249</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.827996033806823</v>
       </c>
       <c r="E3">
-        <v>-12.85898894177823</v>
+        <v>-9.245416123299542</v>
       </c>
       <c r="F3">
-        <v>-2.683626402298746</v>
+        <v>-2.004660859165951</v>
       </c>
       <c r="G3">
-        <v>-7.520125586418358</v>
+        <v>-5.502814165563949</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.035914207815235</v>
       </c>
       <c r="E4">
-        <v>-12.85854062285147</v>
+        <v>-10.41338202546185</v>
       </c>
       <c r="F4">
-        <v>-2.375626148059445</v>
+        <v>-1.513789388717228</v>
       </c>
       <c r="G4">
-        <v>-7.461841247857941</v>
+        <v>-5.550510002152038</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.226155968658029</v>
       </c>
       <c r="E5">
-        <v>-13.14768821671523</v>
+        <v>-10.83320326529095</v>
       </c>
       <c r="F5">
-        <v>-2.502749066427862</v>
+        <v>-1.339312019400374</v>
       </c>
       <c r="G5">
-        <v>-7.333240331278625</v>
+        <v>-4.635787461917837</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.355634923496613</v>
       </c>
       <c r="E6">
-        <v>-13.53073824760205</v>
+        <v>-10.45561457405738</v>
       </c>
       <c r="F6">
-        <v>-2.396984773173227</v>
+        <v>-1.544800979175833</v>
       </c>
       <c r="G6">
-        <v>-7.274873962179222</v>
+        <v>-4.764903530281987</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.377036582447372</v>
       </c>
       <c r="E7">
-        <v>-13.79158287891787</v>
+        <v>-11.61678776520819</v>
       </c>
       <c r="F7">
-        <v>-2.331291096294212</v>
+        <v>-1.151797803898261</v>
       </c>
       <c r="G7">
-        <v>-6.972214085536041</v>
+        <v>-5.032188557292794</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.251112780895875</v>
       </c>
       <c r="E8">
-        <v>-14.09470987204331</v>
+        <v>-13.0859696444647</v>
       </c>
       <c r="F8">
-        <v>-2.257262386608229</v>
+        <v>-1.153575480344669</v>
       </c>
       <c r="G8">
-        <v>-6.627735040117738</v>
+        <v>-4.764493377587056</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.951063689087997</v>
       </c>
       <c r="E9">
-        <v>-15.2970287780278</v>
+        <v>-11.39047274820085</v>
       </c>
       <c r="F9">
-        <v>-2.185857116486912</v>
+        <v>-1.293869440417598</v>
       </c>
       <c r="G9">
-        <v>-6.463303184109285</v>
+        <v>-4.4870989069516</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.472555608218103</v>
       </c>
       <c r="E10">
-        <v>-15.60003350235503</v>
+        <v>-13.51928120836264</v>
       </c>
       <c r="F10">
-        <v>-2.187618225585263</v>
+        <v>-1.460460752059801</v>
       </c>
       <c r="G10">
-        <v>-6.606541630065284</v>
+        <v>-4.037263118481086</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.823965084203945</v>
       </c>
       <c r="E11">
-        <v>-15.68306307328567</v>
+        <v>-14.97281720992265</v>
       </c>
       <c r="F11">
-        <v>-2.091152356427052</v>
+        <v>-0.9546297946839224</v>
       </c>
       <c r="G11">
-        <v>-6.110827801750615</v>
+        <v>-3.817700177830843</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.038031201210242</v>
       </c>
       <c r="E12">
-        <v>-16.5962932555685</v>
+        <v>-13.45491347881761</v>
       </c>
       <c r="F12">
-        <v>-1.895326302405249</v>
+        <v>-1.267895152135417</v>
       </c>
       <c r="G12">
-        <v>-6.033784719534853</v>
+        <v>-4.019104838371119</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.151289693118582</v>
       </c>
       <c r="E13">
-        <v>-17.13102452334223</v>
+        <v>-14.50218649172749</v>
       </c>
       <c r="F13">
-        <v>-1.567180981297267</v>
+        <v>-1.316422571326218</v>
       </c>
       <c r="G13">
-        <v>-5.300566231082896</v>
+        <v>-2.557402664177484</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.221623369346116</v>
       </c>
       <c r="E14">
-        <v>-18.96457647820392</v>
+        <v>-16.16236129073151</v>
       </c>
       <c r="F14">
-        <v>-1.812024848012328</v>
+        <v>-0.8470679441652122</v>
       </c>
       <c r="G14">
-        <v>-5.316089690280629</v>
+        <v>-3.161711801223536</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.304270476903207</v>
       </c>
       <c r="E15">
-        <v>-19.42933376561113</v>
+        <v>-16.55633852939883</v>
       </c>
       <c r="F15">
-        <v>-1.584047369985668</v>
+        <v>-0.3505619186426474</v>
       </c>
       <c r="G15">
-        <v>-5.11133490252816</v>
+        <v>-2.640601318038764</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.453336827619279</v>
       </c>
       <c r="E16">
-        <v>-19.90842367325261</v>
+        <v>-17.25985508038645</v>
       </c>
       <c r="F16">
-        <v>-1.267444520268294</v>
+        <v>-0.279119371988204</v>
       </c>
       <c r="G16">
-        <v>-4.49873739982295</v>
+        <v>-2.423952102133308</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.712301168509719</v>
       </c>
       <c r="E17">
-        <v>-21.04198675837864</v>
+        <v>-18.25545820486881</v>
       </c>
       <c r="F17">
-        <v>-0.9586796829162092</v>
+        <v>0.5685763274208225</v>
       </c>
       <c r="G17">
-        <v>-4.516931773370072</v>
+        <v>-0.6693352793280436</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.102355241641954</v>
       </c>
       <c r="E18">
-        <v>-21.24789647150742</v>
+        <v>-19.58428908920559</v>
       </c>
       <c r="F18">
-        <v>-0.4490407205896609</v>
+        <v>0.5190175908135365</v>
       </c>
       <c r="G18">
-        <v>-3.903048031813559</v>
+        <v>-1.047118723574711</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.6350663611493991</v>
       </c>
       <c r="E19">
-        <v>-21.3139487933833</v>
+        <v>-18.81061741889114</v>
       </c>
       <c r="F19">
-        <v>-0.3360248990909188</v>
+        <v>0.4592293451490794</v>
       </c>
       <c r="G19">
-        <v>-4.055388586375458</v>
+        <v>-1.031900417982006</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.2964646933281075</v>
       </c>
       <c r="E20">
-        <v>-22.27561553365218</v>
+        <v>-17.7050357746585</v>
       </c>
       <c r="F20">
-        <v>0.06939467518721523</v>
+        <v>0.7717905903081944</v>
       </c>
       <c r="G20">
-        <v>-3.632370221710286</v>
+        <v>-0.6440337798831653</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.07181124087380025</v>
       </c>
       <c r="E21">
-        <v>-22.44528386929756</v>
+        <v>-21.41138796860634</v>
       </c>
       <c r="F21">
-        <v>0.1116347857907676</v>
+        <v>0.710169167581342</v>
       </c>
       <c r="G21">
-        <v>-3.05692270950111</v>
+        <v>-1.476722499909689</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.06519212023089185</v>
       </c>
       <c r="E22">
-        <v>-23.03556139924937</v>
+        <v>-20.93078102217229</v>
       </c>
       <c r="F22">
-        <v>0.1530075957235889</v>
+        <v>1.559481840160633</v>
       </c>
       <c r="G22">
-        <v>-3.295933450334182</v>
+        <v>-1.441282025846126</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.1395530660235834</v>
       </c>
       <c r="E23">
-        <v>-23.3579842201215</v>
+        <v>-22.3794806134921</v>
       </c>
       <c r="F23">
-        <v>0.2706722150868419</v>
+        <v>1.305492797318665</v>
       </c>
       <c r="G23">
-        <v>-3.79608677141878</v>
+        <v>-1.566089850302725</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.1724374348438281</v>
       </c>
       <c r="E24">
-        <v>-24.65867969544862</v>
+        <v>-21.42544888040016</v>
       </c>
       <c r="F24">
-        <v>0.4974270228269702</v>
+        <v>2.153616762674939</v>
       </c>
       <c r="G24">
-        <v>-3.272850056663488</v>
+        <v>-1.323758513251495</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.1845367171128213</v>
       </c>
       <c r="E25">
-        <v>-24.61422819458933</v>
+        <v>-22.55977274915948</v>
       </c>
       <c r="F25">
-        <v>0.8167378055840956</v>
+        <v>1.534451890717643</v>
       </c>
       <c r="G25">
-        <v>-3.806117465726003</v>
+        <v>0.01822829234579939</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.1879994266141609</v>
       </c>
       <c r="E26">
-        <v>-24.04829574090275</v>
+        <v>-22.92916490243916</v>
       </c>
       <c r="F26">
-        <v>0.655102616112842</v>
+        <v>1.83487589669094</v>
       </c>
       <c r="G26">
-        <v>-3.066261066059289</v>
+        <v>-1.813375831908717</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.1940463831691737</v>
       </c>
       <c r="E27">
-        <v>-24.57917780576996</v>
+        <v>-22.28889301944266</v>
       </c>
       <c r="F27">
-        <v>0.5760531715984909</v>
+        <v>1.507968984850143</v>
       </c>
       <c r="G27">
-        <v>-3.665887899940014</v>
+        <v>-1.010989192983665</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.2050145873483242</v>
       </c>
       <c r="E28">
-        <v>-24.7636361375244</v>
+        <v>-22.50596994947435</v>
       </c>
       <c r="F28">
-        <v>0.5273062350459483</v>
+        <v>1.819902327517936</v>
       </c>
       <c r="G28">
-        <v>-3.80814526064974</v>
+        <v>-1.526977689314144</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.2202593722445094</v>
       </c>
       <c r="E29">
-        <v>-22.98151406196783</v>
+        <v>-20.68243497911763</v>
       </c>
       <c r="F29">
-        <v>0.3612732430332322</v>
+        <v>1.755170385193572</v>
       </c>
       <c r="G29">
-        <v>-3.951049022006676</v>
+        <v>-2.127037644440715</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.2353082155163784</v>
       </c>
       <c r="E30">
-        <v>-23.58219349671526</v>
+        <v>-22.33885567316929</v>
       </c>
       <c r="F30">
-        <v>0.7107664204787605</v>
+        <v>2.24527727252951</v>
       </c>
       <c r="G30">
-        <v>-3.328850665018531</v>
+        <v>-0.5219789003149409</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.2442821470485458</v>
       </c>
       <c r="E31">
-        <v>-23.04251713532516</v>
+        <v>-22.1122100775594</v>
       </c>
       <c r="F31">
-        <v>0.5405236653250173</v>
+        <v>1.661023116395796</v>
       </c>
       <c r="G31">
-        <v>-3.170213446284058</v>
+        <v>-0.5406654570959785</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.2419382465981807</v>
       </c>
       <c r="E32">
-        <v>-22.99124122413631</v>
+        <v>-21.34804820266105</v>
       </c>
       <c r="F32">
-        <v>0.3721339680513365</v>
+        <v>1.359427798914941</v>
       </c>
       <c r="G32">
-        <v>-3.426007635393689</v>
+        <v>-2.80454755325642</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.2258462953965422</v>
       </c>
       <c r="E33">
-        <v>-22.40621672403339</v>
+        <v>-20.37472517029644</v>
       </c>
       <c r="F33">
-        <v>0.01167817639715968</v>
+        <v>1.302828767751262</v>
       </c>
       <c r="G33">
-        <v>-3.313737358515729</v>
+        <v>-0.5472082128855112</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.1981695193838968</v>
       </c>
       <c r="E34">
-        <v>-22.0756652923175</v>
+        <v>-19.72536463996654</v>
       </c>
       <c r="F34">
-        <v>-0.1077318130837919</v>
+        <v>1.875424481057976</v>
       </c>
       <c r="G34">
-        <v>-3.427740120377076</v>
+        <v>-2.02844678024408</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.1650270427676059</v>
       </c>
       <c r="E35">
-        <v>-21.5257817505141</v>
+        <v>-20.34709242190163</v>
       </c>
       <c r="F35">
-        <v>0.1440628845081599</v>
+        <v>1.697756240505538</v>
       </c>
       <c r="G35">
-        <v>-4.004224498599037</v>
+        <v>-2.081701006153867</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.1344629268576484</v>
       </c>
       <c r="E36">
-        <v>-21.17135167535577</v>
+        <v>-17.82177983457624</v>
       </c>
       <c r="F36">
-        <v>0.4398563166998073</v>
+        <v>2.013208487900423</v>
       </c>
       <c r="G36">
-        <v>-3.59724802613799</v>
+        <v>-0.7937395135328306</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.112755954882929</v>
       </c>
       <c r="E37">
-        <v>-20.94037685859454</v>
+        <v>-18.96860229159673</v>
       </c>
       <c r="F37">
-        <v>0.218212535834952</v>
+        <v>1.952432828291829</v>
       </c>
       <c r="G37">
-        <v>-3.656779228890996</v>
+        <v>-2.135191480015935</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.1021678437643712</v>
       </c>
       <c r="E38">
-        <v>-21.16559598489202</v>
+        <v>-19.51794241651921</v>
       </c>
       <c r="F38">
-        <v>0.2312758897771002</v>
+        <v>1.02197079983209</v>
       </c>
       <c r="G38">
-        <v>-3.605707015318238</v>
+        <v>-0.7296638189199941</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.09998686676493751</v>
       </c>
       <c r="E39">
-        <v>-20.3052719644408</v>
+        <v>-18.78171669777419</v>
       </c>
       <c r="F39">
-        <v>0.2683743239114761</v>
+        <v>1.879606079707308</v>
       </c>
       <c r="G39">
-        <v>-3.667436636516072</v>
+        <v>-0.9724610894326653</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.1013024389823555</v>
       </c>
       <c r="E40">
-        <v>-19.37073531195187</v>
+        <v>-18.3056382253478</v>
       </c>
       <c r="F40">
-        <v>0.2210372686784983</v>
+        <v>1.708629391034684</v>
       </c>
       <c r="G40">
-        <v>-3.375883694851612</v>
+        <v>-0.8605320595968872</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.100211829191668</v>
       </c>
       <c r="E41">
-        <v>-18.56215363551229</v>
+        <v>-16.43506146699941</v>
       </c>
       <c r="F41">
-        <v>0.1279155187253891</v>
+        <v>1.413039737224125</v>
       </c>
       <c r="G41">
-        <v>-3.251958518994504</v>
+        <v>-0.6696437141546314</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.09174800286323304</v>
       </c>
       <c r="E42">
-        <v>-18.89279563670833</v>
+        <v>-16.86603180983539</v>
       </c>
       <c r="F42">
-        <v>-0.1347200230669998</v>
+        <v>0.8462525361458419</v>
       </c>
       <c r="G42">
-        <v>-3.852825654624699</v>
+        <v>-1.325641934426616</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.07334943489424242</v>
       </c>
       <c r="E43">
-        <v>-18.30627221170888</v>
+        <v>-16.06797883546364</v>
       </c>
       <c r="F43">
-        <v>0.3145541498827429</v>
+        <v>1.122947129498544</v>
       </c>
       <c r="G43">
-        <v>-3.884341787703165</v>
+        <v>-1.755455708941398</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.04608326944879372</v>
       </c>
       <c r="E44">
-        <v>-18.37907195985618</v>
+        <v>-16.29435725110708</v>
       </c>
       <c r="F44">
-        <v>-0.0575542860266146</v>
+        <v>0.9009065606477478</v>
       </c>
       <c r="G44">
-        <v>-3.779290198255983</v>
+        <v>-0.6009874342448102</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.01537493482829632</v>
       </c>
       <c r="E45">
-        <v>-16.65464264315733</v>
+        <v>-15.65475105378971</v>
       </c>
       <c r="F45">
-        <v>0.201541641853612</v>
+        <v>1.133399469387068</v>
       </c>
       <c r="G45">
-        <v>-4.12203019624778</v>
+        <v>-0.5480088309460157</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.009866078582986609</v>
       </c>
       <c r="E46">
-        <v>-16.67771068975241</v>
+        <v>-14.09300716581642</v>
       </c>
       <c r="F46">
-        <v>0.3723543137804812</v>
+        <v>1.089567236635335</v>
       </c>
       <c r="G46">
-        <v>-4.224161498507057</v>
+        <v>-0.2056035175532813</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.01979288880578771</v>
       </c>
       <c r="E47">
-        <v>-16.2617794090959</v>
+        <v>-14.74291111302723</v>
       </c>
       <c r="F47">
-        <v>0.09313651331885187</v>
+        <v>1.114191286050953</v>
       </c>
       <c r="G47">
-        <v>-3.348790648435277</v>
+        <v>-0.8362543012785557</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.005235128802323622</v>
       </c>
       <c r="E48">
-        <v>-16.28809437155448</v>
+        <v>-13.7291397508261</v>
       </c>
       <c r="F48">
-        <v>-0.02701155151799403</v>
+        <v>1.159990063016932</v>
       </c>
       <c r="G48">
-        <v>-3.734770584137437</v>
+        <v>-0.9266782050137332</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.03883974485099707</v>
       </c>
       <c r="E49">
-        <v>-15.25890808383123</v>
+        <v>-14.15023349185135</v>
       </c>
       <c r="F49">
-        <v>-0.155108629952104</v>
+        <v>0.6534715606967298</v>
       </c>
       <c r="G49">
-        <v>-3.785111085302438</v>
+        <v>-0.9305598901185562</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.1140674144335756</v>
       </c>
       <c r="E50">
-        <v>-14.87588069531446</v>
+        <v>-13.17495415871542</v>
       </c>
       <c r="F50">
-        <v>-0.1138700155385362</v>
+        <v>0.6290910512975348</v>
       </c>
       <c r="G50">
-        <v>-4.091203119696798</v>
+        <v>-1.73222137907897</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.2175715112638573</v>
       </c>
       <c r="E51">
-        <v>-14.59123893308833</v>
+        <v>-11.47774097080267</v>
       </c>
       <c r="F51">
-        <v>-0.1232637018862826</v>
+        <v>0.5407738322806627</v>
       </c>
       <c r="G51">
-        <v>-3.969391050523972</v>
+        <v>-0.9276691339246855</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.3431431255148724</v>
       </c>
       <c r="E52">
-        <v>-13.94804165588288</v>
+        <v>-11.49569184176907</v>
       </c>
       <c r="F52">
-        <v>0.0732954572869981</v>
+        <v>0.352341785696248</v>
       </c>
       <c r="G52">
-        <v>-4.511399633820847</v>
+        <v>-1.237993944130729</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.4825461385488785</v>
       </c>
       <c r="E53">
-        <v>-12.17420215928634</v>
+        <v>-12.46059644095343</v>
       </c>
       <c r="F53">
-        <v>-0.181914599106696</v>
+        <v>1.08200258551297</v>
       </c>
       <c r="G53">
-        <v>-4.647698296178621</v>
+        <v>-1.087018377737559</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.6250054277692616</v>
       </c>
       <c r="E54">
-        <v>-12.76995914278744</v>
+        <v>-11.29723599685693</v>
       </c>
       <c r="F54">
-        <v>-0.2918745732565108</v>
+        <v>-0.1067104360761401</v>
       </c>
       <c r="G54">
-        <v>-3.765049696687993</v>
+        <v>-0.8556003835930417</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.7608472415013464</v>
       </c>
       <c r="E55">
-        <v>-11.81931923672724</v>
+        <v>-11.07331201412564</v>
       </c>
       <c r="F55">
-        <v>-0.008387367200852746</v>
+        <v>0.7385979084780182</v>
       </c>
       <c r="G55">
-        <v>-4.73173366153756</v>
+        <v>-1.58792309855927</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.8808365513141894</v>
       </c>
       <c r="E56">
-        <v>-11.86653310673121</v>
+        <v>-9.846136314313046</v>
       </c>
       <c r="F56">
-        <v>-0.3382780584265335</v>
+        <v>0.6259780465978142</v>
       </c>
       <c r="G56">
-        <v>-4.695823972790997</v>
+        <v>-3.05916378382621</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.9784091571910982</v>
       </c>
       <c r="E57">
-        <v>-11.20686576955986</v>
+        <v>-9.705404927576673</v>
       </c>
       <c r="F57">
-        <v>-0.3089232027735274</v>
+        <v>0.6757629275060646</v>
       </c>
       <c r="G57">
-        <v>-5.095181448791013</v>
+        <v>-0.3652086966477912</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.048066177352438</v>
       </c>
       <c r="E58">
-        <v>-12.01491761454054</v>
+        <v>-8.404609825821378</v>
       </c>
       <c r="F58">
-        <v>-0.3687810312998197</v>
+        <v>0.2412651722874594</v>
       </c>
       <c r="G58">
-        <v>-5.618309883234843</v>
+        <v>-2.38470541106079</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.086158314664478</v>
       </c>
       <c r="E59">
-        <v>-11.45154374866829</v>
+        <v>-8.928042550945973</v>
       </c>
       <c r="F59">
-        <v>-0.2111882747542277</v>
+        <v>0.5203148141663205</v>
       </c>
       <c r="G59">
-        <v>-4.905959963900956</v>
+        <v>-1.709725324067417</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.092457737075602</v>
       </c>
       <c r="E60">
-        <v>-10.69448252101398</v>
+        <v>-8.700894294721227</v>
       </c>
       <c r="F60">
-        <v>-0.7695774871029296</v>
+        <v>0.3114734515117316</v>
       </c>
       <c r="G60">
-        <v>-4.972637667210432</v>
+        <v>-1.479849504055839</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.069419552017306</v>
       </c>
       <c r="E61">
-        <v>-10.03736471470895</v>
+        <v>-8.892983105178589</v>
       </c>
       <c r="F61">
-        <v>-0.362879741922276</v>
+        <v>-0.2248290007761272</v>
       </c>
       <c r="G61">
-        <v>-5.48413745244759</v>
+        <v>-1.832488947492482</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.022707300030379</v>
       </c>
       <c r="E62">
-        <v>-9.986174844526243</v>
+        <v>-8.028397790686149</v>
       </c>
       <c r="F62">
-        <v>-0.7738228700422771</v>
+        <v>0.8826924181949922</v>
       </c>
       <c r="G62">
-        <v>-5.081580785427115</v>
+        <v>-2.436328869855533</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.959076214006415</v>
       </c>
       <c r="E63">
-        <v>-9.687970302647143</v>
+        <v>-8.242698766151133</v>
       </c>
       <c r="F63">
-        <v>-0.4935058260371328</v>
+        <v>0.2445355667937119</v>
       </c>
       <c r="G63">
-        <v>-5.615107410992826</v>
+        <v>-1.942495181494426</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.8859147935381775</v>
       </c>
       <c r="E64">
-        <v>-9.764967946199562</v>
+        <v>-9.173825477712281</v>
       </c>
       <c r="F64">
-        <v>-0.971451451532572</v>
+        <v>0.0007462117824146024</v>
       </c>
       <c r="G64">
-        <v>-6.036153761500771</v>
+        <v>-2.047274429552174</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.810215109171845</v>
       </c>
       <c r="E65">
-        <v>-9.406398845798215</v>
+        <v>-7.58990112404942</v>
       </c>
       <c r="F65">
-        <v>-0.7099383475709764</v>
+        <v>-0.3495803032703299</v>
       </c>
       <c r="G65">
-        <v>-5.399468811327679</v>
+        <v>-3.561784583523512</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.7401993766722466</v>
       </c>
       <c r="E66">
-        <v>-9.229317398202273</v>
+        <v>-6.783991247274365</v>
       </c>
       <c r="F66">
-        <v>-1.186460837868406</v>
+        <v>-0.3183558223892053</v>
       </c>
       <c r="G66">
-        <v>-5.732391394413618</v>
+        <v>-3.184752539013957</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.6843179161577837</v>
       </c>
       <c r="E67">
-        <v>-8.391767073535625</v>
+        <v>-6.481194832751487</v>
       </c>
       <c r="F67">
-        <v>-1.073992567222914</v>
+        <v>-0.09302332147968384</v>
       </c>
       <c r="G67">
-        <v>-5.031394501675408</v>
+        <v>-2.491604328245939</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.6488990142405763</v>
       </c>
       <c r="E68">
-        <v>-9.263588889492324</v>
+        <v>-8.303887506942775</v>
       </c>
       <c r="F68">
-        <v>-1.038995701189441</v>
+        <v>-0.2024340880414425</v>
       </c>
       <c r="G68">
-        <v>-6.168439489891345</v>
+        <v>-3.604512650670601</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.6375242506136347</v>
       </c>
       <c r="E69">
-        <v>-9.215460267738802</v>
+        <v>-7.338634215259823</v>
       </c>
       <c r="F69">
-        <v>-1.138163704815584</v>
+        <v>-0.3684728786259782</v>
       </c>
       <c r="G69">
-        <v>-6.167130282489127</v>
+        <v>-3.416715215937342</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.6509728108391033</v>
       </c>
       <c r="E70">
-        <v>-9.368205696017524</v>
+        <v>-7.384054809556757</v>
       </c>
       <c r="F70">
-        <v>-1.309422866772562</v>
+        <v>-0.6749423099049058</v>
       </c>
       <c r="G70">
-        <v>-5.427792315828805</v>
+        <v>-2.834839790693213</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.6885448801747261</v>
       </c>
       <c r="E71">
-        <v>-9.12288014512599</v>
+        <v>-7.184969506757544</v>
       </c>
       <c r="F71">
-        <v>-1.595797761594379</v>
+        <v>-0.357789424232073</v>
       </c>
       <c r="G71">
-        <v>-5.477207512514043</v>
+        <v>-3.330419088923946</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.7468630794255621</v>
       </c>
       <c r="E72">
-        <v>-9.819214536337444</v>
+        <v>-7.844537217500724</v>
       </c>
       <c r="F72">
-        <v>-1.269982637990472</v>
+        <v>-1.207861709719731</v>
       </c>
       <c r="G72">
-        <v>-5.117077040257188</v>
+        <v>-4.047963181986435</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.8202577863787766</v>
       </c>
       <c r="E73">
-        <v>-9.707071406011496</v>
+        <v>-7.209482136561064</v>
       </c>
       <c r="F73">
-        <v>-1.912504157237103</v>
+        <v>-0.9040041208618306</v>
       </c>
       <c r="G73">
-        <v>-4.939195457076571</v>
+        <v>-3.397812098533381</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.900425192350255</v>
       </c>
       <c r="E74">
-        <v>-10.57667426970444</v>
+        <v>-8.321602897260782</v>
       </c>
       <c r="F74">
-        <v>-2.005363314723525</v>
+        <v>-1.068515401955604</v>
       </c>
       <c r="G74">
-        <v>-4.862592058549775</v>
+        <v>-2.622226477305874</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.9788151619166934</v>
       </c>
       <c r="E75">
-        <v>-10.31805311912638</v>
+        <v>-7.833872661212661</v>
       </c>
       <c r="F75">
-        <v>-1.950471548777015</v>
+        <v>-0.5981501665631832</v>
       </c>
       <c r="G75">
-        <v>-4.706884970667885</v>
+        <v>-2.077940726246744</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.047340666318502</v>
       </c>
       <c r="E76">
-        <v>-10.87882764091822</v>
+        <v>-8.791092440006006</v>
       </c>
       <c r="F76">
-        <v>-1.678231915316569</v>
+        <v>-0.9638097622417465</v>
       </c>
       <c r="G76">
-        <v>-4.385558224573024</v>
+        <v>-1.896515423781927</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.099281576714284</v>
       </c>
       <c r="E77">
-        <v>-10.47417678901482</v>
+        <v>-8.82037808141361</v>
       </c>
       <c r="F77">
-        <v>-1.978234282281841</v>
+        <v>-1.562883411211543</v>
       </c>
       <c r="G77">
-        <v>-4.991918125093728</v>
+        <v>-2.04576178641327</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.130560994476844</v>
       </c>
       <c r="E78">
-        <v>-11.03052246322717</v>
+        <v>-9.492842886130635</v>
       </c>
       <c r="F78">
-        <v>-1.785869147268934</v>
+        <v>-1.175840339397114</v>
       </c>
       <c r="G78">
-        <v>-4.154323978835835</v>
+        <v>-2.49567632420121</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.138019917057814</v>
       </c>
       <c r="E79">
-        <v>-11.53374913732953</v>
+        <v>-11.73346389801581</v>
       </c>
       <c r="F79">
-        <v>-1.955005203572537</v>
+        <v>-0.9836972068481571</v>
       </c>
       <c r="G79">
-        <v>-3.695271239004842</v>
+        <v>-3.76152238351159</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.119661600855367</v>
       </c>
       <c r="E80">
-        <v>-11.80052154112139</v>
+        <v>-9.607435920894734</v>
       </c>
       <c r="F80">
-        <v>-2.016008664216901</v>
+        <v>-1.513068709076792</v>
       </c>
       <c r="G80">
-        <v>-3.950350121814514</v>
+        <v>-1.84195527169148</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.070963765984356</v>
       </c>
       <c r="E81">
-        <v>-12.11846117272592</v>
+        <v>-10.16732286178107</v>
       </c>
       <c r="F81">
-        <v>-1.901725440591876</v>
+        <v>-2.01355835343942</v>
       </c>
       <c r="G81">
-        <v>-3.299319670983529</v>
+        <v>-2.169634462725427</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.9888832607183653</v>
       </c>
       <c r="E82">
-        <v>-14.41002298872339</v>
+        <v>-12.23420443988797</v>
       </c>
       <c r="F82">
-        <v>-2.126579973509982</v>
+        <v>-1.943794907510451</v>
       </c>
       <c r="G82">
-        <v>-3.593986491907902</v>
+        <v>-2.62762408677116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.8687456058015719</v>
       </c>
       <c r="E83">
-        <v>-13.89047569429737</v>
+        <v>-12.94688662226712</v>
       </c>
       <c r="F83">
-        <v>-2.370985633868962</v>
+        <v>-1.531580235427153</v>
       </c>
       <c r="G83">
-        <v>-3.117874681189355</v>
+        <v>-2.329111674179118</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.7093402281799965</v>
       </c>
       <c r="E84">
-        <v>-15.65174414704862</v>
+        <v>-14.15949422119704</v>
       </c>
       <c r="F84">
-        <v>-2.568893375174</v>
+        <v>-1.327406723087339</v>
       </c>
       <c r="G84">
-        <v>-4.188143529449032</v>
+        <v>-1.667335222740951</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.5121223060129304</v>
       </c>
       <c r="E85">
-        <v>-15.66305627511978</v>
+        <v>-14.82786075693712</v>
       </c>
       <c r="F85">
-        <v>-2.327628055639033</v>
+        <v>-1.538758038972411</v>
       </c>
       <c r="G85">
-        <v>-2.810712968566616</v>
+        <v>-1.438492987520598</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.2779462780076539</v>
       </c>
       <c r="E86">
-        <v>-17.27392504912828</v>
+        <v>-15.6924687137996</v>
       </c>
       <c r="F86">
-        <v>-2.703618221197909</v>
+        <v>-1.933150386384478</v>
       </c>
       <c r="G86">
-        <v>-2.768808488030948</v>
+        <v>-0.5834197740155431</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.01061477029826578</v>
       </c>
       <c r="E87">
-        <v>-18.56354840550665</v>
+        <v>-17.44034194043616</v>
       </c>
       <c r="F87">
-        <v>-2.738458525792253</v>
+        <v>-1.574036549922836</v>
       </c>
       <c r="G87">
-        <v>-2.986258321996909</v>
+        <v>-2.120150360387441</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.2905183960045911</v>
       </c>
       <c r="E88">
-        <v>-19.74924328340899</v>
+        <v>-17.78718229315764</v>
       </c>
       <c r="F88">
-        <v>-2.696228355597535</v>
+        <v>-1.942769388665786</v>
       </c>
       <c r="G88">
-        <v>-2.659281312376683</v>
+        <v>-1.322324619430018</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.6184915667106461</v>
       </c>
       <c r="E89">
-        <v>-21.75907967444126</v>
+        <v>-21.07482725188227</v>
       </c>
       <c r="F89">
-        <v>-2.985341833053007</v>
+        <v>-1.905580662484504</v>
       </c>
       <c r="G89">
-        <v>-2.537853146126313</v>
+        <v>-1.144869595052128</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.9678687778862598</v>
       </c>
       <c r="E90">
-        <v>-22.45667750990086</v>
+        <v>-23.48109984296803</v>
       </c>
       <c r="F90">
-        <v>-3.109796580017008</v>
+        <v>-1.550744515290919</v>
       </c>
       <c r="G90">
-        <v>-2.957052168896291</v>
+        <v>-1.753801973275438</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.329986863555422</v>
       </c>
       <c r="E91">
-        <v>-24.48718185630414</v>
+        <v>-22.59210605357425</v>
       </c>
       <c r="F91">
-        <v>-2.980542272321186</v>
+        <v>-2.354418285812972</v>
       </c>
       <c r="G91">
-        <v>-2.43729354899401</v>
+        <v>-0.1262438929165514</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.695339591110682</v>
       </c>
       <c r="E92">
-        <v>-26.22952128770332</v>
+        <v>-25.68470510831451</v>
       </c>
       <c r="F92">
-        <v>-3.369727502239256</v>
+        <v>-2.026021969381941</v>
       </c>
       <c r="G92">
-        <v>-2.79840182527558</v>
+        <v>-1.611354301715265</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.056379704921716</v>
       </c>
       <c r="E93">
-        <v>-28.214799764192</v>
+        <v>-26.50432720438479</v>
       </c>
       <c r="F93">
-        <v>-3.492875085441639</v>
+        <v>-2.796682813800225</v>
       </c>
       <c r="G93">
-        <v>-2.785267095373122</v>
+        <v>-1.741717234272003</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.401651107127891</v>
       </c>
       <c r="E94">
-        <v>-29.87534816230165</v>
+        <v>-28.87216663656745</v>
       </c>
       <c r="F94">
-        <v>-3.764949045421525</v>
+        <v>-2.665239131058805</v>
       </c>
       <c r="G94">
-        <v>-3.144573981018556</v>
+        <v>-0.8336358864741188</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.72741297842357</v>
       </c>
       <c r="E95">
-        <v>-32.04734467907459</v>
+        <v>-32.15333587746112</v>
       </c>
       <c r="F95">
-        <v>-3.375217093017608</v>
+        <v>-2.618675770980042</v>
       </c>
       <c r="G95">
-        <v>-2.956986544465102</v>
+        <v>-2.287873281620017</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.026446403048821</v>
       </c>
       <c r="E96">
-        <v>-33.99328656609564</v>
+        <v>-33.27322297108399</v>
       </c>
       <c r="F96">
-        <v>-3.542187796930294</v>
+        <v>-2.729397843140432</v>
       </c>
       <c r="G96">
-        <v>-2.977864957247849</v>
+        <v>-2.146731536240502</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.297448630865803</v>
       </c>
       <c r="E97">
-        <v>-36.69059965318036</v>
+        <v>-36.71747388217889</v>
       </c>
       <c r="F97">
-        <v>-3.677162809909848</v>
+        <v>-3.21345350659892</v>
       </c>
       <c r="G97">
-        <v>-3.437062070827459</v>
+        <v>-1.529605947783259</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.538903834109664</v>
       </c>
       <c r="E98">
-        <v>-39.19718700048404</v>
+        <v>-37.03689432478392</v>
       </c>
       <c r="F98">
-        <v>-3.963203872668336</v>
+        <v>-3.438328748702097</v>
       </c>
       <c r="G98">
-        <v>-3.91994304162314</v>
+        <v>-0.6369200915422892</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.745557977559671</v>
       </c>
       <c r="E99">
-        <v>-41.46818048753866</v>
+        <v>-42.71209569152061</v>
       </c>
       <c r="F99">
-        <v>-4.113832544458593</v>
+        <v>-3.283704032560736</v>
       </c>
       <c r="G99">
-        <v>-3.570968722668397</v>
+        <v>-2.208280690252566</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.916201243407869</v>
       </c>
       <c r="E100">
-        <v>-44.2371770539278</v>
+        <v>-43.44972976568202</v>
       </c>
       <c r="F100">
-        <v>-4.299997349461545</v>
+        <v>-2.902096707643476</v>
       </c>
       <c r="G100">
-        <v>-3.911467646335094</v>
+        <v>-1.751931676986555</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.038292263262438</v>
       </c>
       <c r="E101">
-        <v>-46.22128039141149</v>
+        <v>-44.62108749487607</v>
       </c>
       <c r="F101">
-        <v>-4.465967385551648</v>
+        <v>-3.961567018680404</v>
       </c>
       <c r="G101">
-        <v>-4.146836231237183</v>
+        <v>-2.579383567404204</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.113022555186598</v>
       </c>
       <c r="E102">
-        <v>-49.48572824203183</v>
+        <v>-47.52457747505602</v>
       </c>
       <c r="F102">
-        <v>-4.540627311198565</v>
+        <v>-3.664817650505927</v>
       </c>
       <c r="G102">
-        <v>-4.790441277679145</v>
+        <v>-1.722912553514826</v>
       </c>
     </row>
   </sheetData>
